--- a/m2/exemplos/radar-reviews/insumo-reviews-5-lojas.xlsx
+++ b/m2/exemplos/radar-reviews/insumo-reviews-5-lojas.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Beatriz Sampaio</t>
+          <t>Isabella Farias</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -701,19 +701,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>O bowl de cupuaçu virou meu vício, obrigada Maria Pitanga por essa novidade!</t>
+          <t>Loja mais bonita da rede em Fortaleza. Ambiente refrescante, atendimento impecável da Ana e da Priscila.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Lima</t>
+          <t>João Pedro Lima</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Esperei 25 minutos numa quarta 21h. Só tinha 2 pessoas atendendo com fila enorme. Perdi a paciência e fui embora.</t>
+          <t>Bowl de cupuaçu tá dando o que falar mesmo. Só senti que o preço médio ficou um pouco acima do concorrente.</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -753,27 +753,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Fernanda Vieira</t>
+          <t>Nathalia Braga</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Sabor de sempre bom, atendimento ok. Sinto que os preços subiram bastante desde o começo do ano.</t>
+          <t>Peço pelo iFood 3x na semana, sempre entrega direitinho. Loja física também é ótima.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -783,27 +783,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Tiago Mendes</t>
+          <t>Igor Fontes</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Levei os sobrinhos, todos amaram os toppings novos. Atendente super gentil.</t>
+          <t>Cheguei sábado 17h, fila até a rua. Fui embora, voltei domingo. Domingo tudo perfeito, mas sábado é impossível.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -813,27 +813,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Juliana Barbosa</t>
+          <t>Bianca Oliveira</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pagamento pelo app deu erro duas vezes seguidas. No caixa foi rápido. Vocês precisam arrumar esse app.</t>
+          <t>Ana lembrou do meu pedido de sempre sem eu falar. Isso é atendimento nível hotel 5 estrelas.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Marcos Andrade</t>
+          <t>Marcelo Ribeiro</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -851,59 +851,59 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Cupuaçu delicioso, mas o sorbet de manga tava um pouco duro, tive que esperar amolecer.</t>
+          <t>Cupuaçu virou meu vício. Único ponto: a bateria do app pra fidelidade nunca soma direito, sempre preciso reclamar.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ana Paula Cruz</t>
+          <t>Sofia Cardoso</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Cheguei no domingo à tarde e o chão estava pegajoso, mesa suja não limpa. Açaí é bom mas o ambiente afasta.</t>
+          <t>Ambiente familiar mesmo sendo cheio. Levei minha filha pequena e a Ana ainda deu um brinde. Amei.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Rodrigo Silva</t>
+          <t>Vitor Sales</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -911,29 +911,29 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>O açaí em si é excelente, o pessoal simpático. Só precisam melhorar a manutenção da loja, tá desleixada.</t>
+          <t>Loja bem servida de opções, mas o preço realmente subiu. Bowl médio hoje custa quase R$ 30, achei salgado.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Vanessa Oliveira</t>
+          <t>Laís Torres</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -941,29 +941,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Sabor divino, o novo bowl de cupuaçu tá arrasando aqui em Juazeiro. Voltarei sempre!</t>
+          <t>Programa de fidelidade tá gerando resultado — juntei pontos e ganhei um bowl grátis semana passada.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Carlos Eduardo</t>
+          <t>Bernardo Rocha</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -971,269 +971,269 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Açaí bom, mas os banheiros da loja estavam num estado ruim. Falta zelo.</t>
+          <t>Fila enorme quarta-feira à noite. Antes era horário tranquilo, agora tá cheio sempre. Escala de atendimento tá curta.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Renata Alves</t>
+          <t>Priscila Andrade</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Atendimento rápido, sem fila num terça de tarde. Preço tá subindo demais.</t>
+          <t>O melhor da rede. Aline (gerente) sempre atenciosa. Cupuaçu novo virou o pedido oficial da casa.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cariri Garden</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Juazeiro do Norte/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Felipe Martins</t>
+          <t>Antonio Vasques</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Melhor doce da cidade. Único ponto: o app às vezes trava, mas no caixa vão super rápido.</t>
+          <t>Bom produto, bom atendimento, mas o preço tá se distanciando dos concorrentes locais. Cuidado com isso.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Thiago Rodrigues</t>
+          <t>Helena Vieira</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Sorbet chegou tão duro que quebrei a colherzinha tentando comer. Terceira vez que isso acontece nessa loja.</t>
+          <t>Ana e Priscila são as melhores atendentes de qualquer lugar que eu já fui em Fortaleza. Toppings sempre no ponto.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Karina Sousa</t>
+          <t>Guilherme Prado</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Fui atendida pelo Bruno de um jeito grosso, mal olhou pra mim. Não volto mais.</t>
+          <t>Sempre limpo, sempre gostoso. Fila do fim de semana continua sendo o único ponto negativo — hora de expandir o balcão?</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Batista</t>
+          <t>Ana Clara Bezerra</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Açaí ok. O sorbet vem sempre muito congelado, precisa esperar 10 min. Vocês estão errando o freezer?</t>
+          <t>Peguei o combo bowl cupuaçu + café gelado, experiência 10/10. Ambiente confortável para trabalhar.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Larissa Freitas</t>
+          <t>Ricardo Mota</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>O bowl de cupuaçu novo salvou minha experiência aqui, delicioso demais!</t>
+          <t>Tentei pagar pelo app 3 vezes e travou. Tive que refazer no caixa e perdi meu horário. Chatiado.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bruno Cavalcanti</t>
+          <t>Juliane Aragão</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Sorbet duro de novo. Já reclamei da última vez, aparentemente não mudou nada.</t>
+          <t>Cupuaçu com castanha-do-pará é o melhor bowl que já comi. Ana me indicou baseado no que eu tinha pedido antes, arrasou.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Sobral Centro</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sobral/CE</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Amanda Ribeiro</t>
+          <t>Felipe Souto</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Loja limpa, açaí bom. Só que o atendente Bruno é seco, não sorri, parece que tá fazendo favor.</t>
+          <t>Loja moderna, atendimento simpático. O preço tá subindo, mas ainda vale.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>João Marques</t>
+          <t>Luana Cavalcante</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1241,29 +1241,29 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Que saudade! Um pedacinho do Brasil aqui em Lisboa. O bowl de cupuaçu tá idêntico ao do Ceará.</t>
+          <t>Melhor açaí de Fortaleza sem dúvida. Ana no atendimento sempre torna a experiência especial.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sofia Almeida</t>
+          <t>Rodrigo Aguiar</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1271,119 +1271,119 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Achei o açaí muito doce para o paladar português. Meu marido brasileiro amou, eu nem tanto.</t>
+          <t>Sábado 15h fila até a esquina. Fui embora sem esperar. Vocês precisam de mais gente na escala do fim de semana.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Mariana Prata</t>
+          <t>Cintia Barros</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Ambiente lindo, atendimento cortês. Só a fila aos sábados que é uma loucura, uns 30 min de espera.</t>
+          <t>Novidade de cupuaçu chegou e virou hit imediato. Parabéns pela escolha de sabor.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>André Fernandes</t>
+          <t>Otávio Pinheiro</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Melhor açaí de Portugal, sem dúvidas. Tenho vindo toda semana desde que abriu.</t>
+          <t>Bowl e atendimento sempre bons. Preço se tornou um ponto de atenção, tá pertinho de me fazer pensar antes de vir.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Patrícia Nogueira</t>
+          <t>Vanessa Franco</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Preço muito alto comparado ao do Brasil. Um bowl médio aqui custa quase 12 euros, absurdo.</t>
+          <t>Vim comemorar aniversário com as amigas, Ana montou uma vela improvisada no bowl. Detalhes assim ficam guardados.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Iguatemi Lisboa</t>
+          <t>Aldeota</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Lisboa/PT</t>
+          <t>Fortaleza/CE</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Ricardo Sá</t>
+          <t>Thiago Bezerra</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -1391,7 +1391,3607 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
+          <t>Melhor loja da rede que já visitei — visitei Iguatemi e Sobral também. Aqui a operação é impecável, só a fila fim-semana atrapalha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Beatriz Sampaio</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>O bowl de cupuaçu virou meu vício, obrigada Maria Pitanga por essa novidade!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Lima</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Esperei 25 minutos numa quarta 21h. Só tinha 2 pessoas atendendo com fila enorme. Perdi a paciência e fui embora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Fernanda Vieira</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Sabor de sempre bom, atendimento ok. Sinto que os preços subiram bastante desde o começo do ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Tiago Mendes</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Levei os sobrinhos, todos amaram os toppings novos. Atendente super gentil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Juliana Barbosa</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento pelo app deu erro duas vezes seguidas. No caixa foi rápido. Vocês precisam arrumar esse app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Marcos Andrade</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu delicioso, mas o sorbet de manga tava um pouco duro, tive que esperar amolecer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Cordeiro</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Loja lotada em qualquer horário. Bruno (novato) tá bem inseguro no atendimento, cometeu 2 erros no meu pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Alan Pereira</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Fila de 30 min num domingo à noite. Não dá. Precisam abrir uma 2ª unidade no shopping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Michele Gomes</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Bowl bom, mas o sorbet realmente vem gelado demais. Já reclamei uma vez, achei que iam ajustar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Nogueira</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Comprei via iFood, chegou com sorbet totalmente derretido. Sabor bom mas experiência ruim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Renata Peixoto</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu com castanha-do-pará, combo perfeito. Voltarei toda semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Lucas Bento</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Cheguei 20h30 e o cupuaçu já tinha esgotado. 3ª vez que acontece esse mês. Preciso mesmo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Amanda Correia</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Atendimento OK, loja lotada como sempre. Perceptível a queda no atendimento desde que a Ana saiu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo Xavier</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet de manga quebrou minha colherzinha de tão duro. Já é a segunda vez que reclamo isso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Patrícia Lopes</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Bom produto, movimento intenso. Cupuaçu vale a pena, mas prepare-se pra fila em horário de pico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Sales</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento pelo app trava toda vez que eu tento. Ridículo em 2026 ter esse problema recorrente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Karolina Freire</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Loja bem servida de opções veganas, isso pesa positivo. Só o fluxo intenso que atrapalha um pouco a experiência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo Barreto</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Bowl entregue certinho mas 22 min de espera num terça 19h. Escala insuficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Sabrina Melo</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Novo bowl de cupuaçu é obra de arte. Vale a fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Luiz Henrique Cruz</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo (que era bom) saiu, o pessoal novo tá cru. Padrão caiu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Denise Coelho</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Sempre bom mas o app é uma pena. Se resolvessem essa questão eu daria 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Pontes</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Loja produtiva mas o novo atendente Bruno mistura os toppings. 3ª vez que meu pedido veio errado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Aline Sales</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Combo cupuaçu + coco raspa nível divino. Preço médio, atendimento correto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Kaio Melo</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Domingo 14h, esgotou 3 sabores diferentes de sorbet. Vocês estão errando a gestão de estoque?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Lorena Chagas</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Loja lotada em qualquer dia, isso é bom sinal, só sinto que a operação não tá dando conta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Marcelo Feitosa</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Vim 3x essa semana, 3x o app deu erro na hora de pagar. Uma delas o cupuaçu tinha esgotado. Frustrante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Camille Amaral</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Bowl cupuaçu virou meu momento premium da semana. Preço vale, produto entrega.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Rogério Costa</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Cheguei sexta 20h, fila até o corredor do shopping. Fui embora. Vocês precisam repensar horário-pico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Simone Vasconcelos</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Loja com energia boa, mas dá pra sentir que o time novo ainda tá se ajustando. Padrão da rede ainda existe, só oscila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Fortaleza/CE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Jefferson Ramos</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet duro é praticamente marca da casa aqui. Sabor bom, temperatura ruim. Resolvam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Ana Paula Cruz</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Cheguei no domingo à tarde e o chão estava pegajoso, mesa suja não limpa. Açaí é bom mas o ambiente afasta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Silva</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>O açaí em si é excelente, o pessoal simpático. Só precisam melhorar a manutenção da loja, tá desleixada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Oliveira</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Sabor divino, o novo bowl de cupuaçu tá arrasando aqui em Juazeiro. Voltarei sempre!</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Açaí bom, mas os banheiros da loja estavam num estado ruim. Falta zelo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Renata Alves</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Atendimento rápido, sem fila num terça de tarde. Preço tá subindo demais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Felipe Martins</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Melhor doce da cidade. Único ponto: o app às vezes trava, mas no caixa vão super rápido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Bruna Nascimento</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Fui almoçar e tinha 3 mesas sujas. Solicitei limpeza, atendente veio de má vontade. Produto bom, atendimento oscilante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Márcio Duarte</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Bowl de cupuaçu vale a pena. Só melhorem a limpeza do salão em horário pós-almoço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Silvana Barros</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Banheiro sem papel, chão molhado. Salão OK mas a manutenção pesada tá abandonada. Difícil recomendar assim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Erick Menezes</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu com granola caseira é sensacional. Fico feliz que chegou a Juazeiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Talita Pereira</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Loja com bom atendimento nos dias úteis, mas o preço em Juazeiro tá salgado pro público local. Cuidem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Wagner Souza</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Produto bom, mas fila no domingo pós-igreja é impossível. Chegou tarde, esgotou meia dúzia de opções.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Camila Nobre</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Ambiente aconchegante quando limpo. Cupuaçu me conquistou. Só cuidem melhor da manutenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Guilherme Pinto</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Cheguei sábado 16h, banheiro fedorento. Café gelado que pedi tava morno. Padrão da rede aqui não existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Débora Alves</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Bowl bom, atendimento cortês. Só a manutenção da loja precisa de atenção — parece que faz tempo que não passa por reforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Rafael Nunes</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Preço alto pra realidade de Juazeiro. Bowl de 350g custa quase R$ 27, meu almoço custa isso na cidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Amélia Correia</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Levei minhas amigas do coral, todas amaram o cupuaçu. Vamos virar clientes de sábado após ensaio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Anderson Lima</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Bom produto mas o WiFi da loja é péssimo — vim trabalhar aqui e não deu. Pra shopping novo é vergonhoso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Vitória Sampaio</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Atendimento simpático, cupuaçu delicioso. Chão da entrada precisa passar pano com mais frequência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Márcia Freire</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Fui no domingo 19h, várias mesas sujas, funcionários conversando em vez de limpar. Padrão de rede não existe aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Elias Batista</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Melhor doce que abriu no Cariri em anos. Cupuaçu é o carro-chefe agora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Isabelle Rocha</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Loja com potencial gigante, atendimento cordial. Precisam cuidar da limpeza fim de semana e podem ter fã fiel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Douglas Aragão</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Preço já beira R$ 30 no bowl médio. Público de Juazeiro sente muito. Vale reavaliar o mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Karla Andrade</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu com castanha-do-pará é uma explosão. Amei. Ambiente confortável no horário matinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Sales</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Banheiro sem sabonete, sem toalha de papel. Já reclamei há 2 semanas, tudo igual. Onde tá a gerência?</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Julia Cavalcante</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu delicioso, atendimento OK. Preço tá esticado pro perfil da cidade — cuidado com o público local.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Marcelo Barreto</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Peguei o combo cupuaçu grande + café, saí feliz. Só a manutenção do salão que precisa de mais atenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Luciana Prado</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Fila em horário pós-missa domingo. Padrão da rede sai um pouco de foco quando a loja fica cheia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Cristian Bezerra</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Bowl com bom sabor, loja com potencial. Faltam ajustes de manutenção — vitrine com poeira, banheiro precário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Cariri Garden</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Juazeiro do Norte/CE</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Nadia Pinheiro</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>3ª vez que venho e encontro loja mal cuidada. Sabor ótimo, mas ambiente não convida a voltar. Perdendo cliente aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Rodrigues</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet chegou tão duro que quebrei a colherzinha tentando comer. Terceira vez que isso acontece nessa loja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Karina Sousa</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Fui atendida pelo Bruno de um jeito grosso, mal olhou pra mim. Não volto mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo Batista</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Açaí ok. O sorbet vem sempre muito congelado, precisa esperar 10 min. Vocês estão errando o freezer?</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Larissa Freitas</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>O bowl de cupuaçu novo salvou minha experiência aqui, delicioso demais!</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Cavalcanti</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet duro de novo. Já reclamei da última vez, aparentemente não mudou nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Amanda Ribeiro</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Loja limpa, açaí bom. Só que o atendente Bruno é seco, não sorri, parece que tá fazendo favor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Fernando Sales</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Bruno atendeu de mau humor total. Chamei o gerente, gerente não apareceu. Última vez que venho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Rosana Barros</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet de manga tão duro que precisei esperar 15 min pra conseguir comer. Segunda vez que isso acontece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Igor Almeida</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Bowl de cupuaçu me impressionou de verdade. Só os problemas de congelamento do sorbet e o atendimento oscilante que atrapalham.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Priscila Aragão</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Cheguei sábado 14h, Bruno atendeu no automático, mal reconheceu que existia. Sorbet tarde da tarde já estava esgotado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Vinícius Melo</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Pior atendimento que já tive em qualquer loja da Maria Pitanga (frequento em Fortaleza e aqui). Bruno é um problema. Gerente ausente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Cíntia Torres</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>O cupuaçu novo é maravilhoso. Só peço pra vocês resolverem o problema do freezer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Marcos Aurélio</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Loja bem localizada, produto bom. Sorbet duro e atendimento do Bruno são pontos que jogam a experiência pra baixo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Wesley Ferreira</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Terceira vez que o sorbet vem pedra. Vocês precisam calibrar o freezer ou trocar por outro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Andreia Silva</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Bowl cupuaçu 10/10. Atendimento oscilante — quando é a Cintia (outra atendente) é ótimo, quando é o Bruno é uma lástima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Neto</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Bruno cortou minha fala, foi grosseiro. Chamei o gerente 3 vezes, ninguém apareceu. Vou reclamar formalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Kaline Vidal</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Loja com bom produto mas atendimento comprometido pela presença do Bruno. Já reclamei antes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Diego Aragão</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu com granola caseira, sensacional. Pena que o resto da experiência com sorbet duro atrapalha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Sabrina Menezes</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet vem sempre gelado demais. Vocês têm alguém na área técnica pra ver a temperatura do freezer?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Otávio Nunes</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Peguei cupuaçu, chegou meio derretido no topping mas duro no meio. Máquinas descalibradas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Larissa Vilas</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Bruno me atendeu com celular na mão. Só perguntou o pedido sem olhar, sem sorrir, sem falar 'obrigado'. Zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Marcelo Aguiar</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu salva a experiência aqui. Sorbet duro continua sendo o problema recorrente. Já é padrão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Denise Barros</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Terceiro sorbet duro seguido nesse mês. Já sei que vou ter que esperar 10 min. Isso é operação ruim, não é 'freezer novo'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Aline Mendes</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Bowl de cupuaçu é o melhor produto novo dos últimos anos. Loja precisa urgente melhorar quesito equipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Elton Cunha</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Bruno é o funcionário mais desagradável que já encontrei. Como esse cara ainda tá empregado?</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Vitor Pereira</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu ótimo. O resto oscila muito — dependendo de quem tá atendendo, a experiência muda 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Clara Rodrigues</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet duro. Bruno grosso. Cupuaçu bom. Padrão de qualidade da rede aqui em Sobral não existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Adriana Lopes</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Cintia atendeu maravilhosamente. Cupuaçu incrível. Estrelas pelo produto e pela Cintia — o resto da equipe precisa melhorar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Rafael Aragão</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Vim 4x nas últimas 3 semanas. Sorbet duro em 3 delas. Bruno atendeu mal em 2. Perdendo cliente antigo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Sobral Centro</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Sobral/CE</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Michele Ramos</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Terrível. Bruno me tratou como se eu estivesse atrapalhando. Nunca mais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>João Marques</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Que saudade! Um pedacinho do Brasil aqui em Lisboa. O bowl de cupuaçu tá idêntico ao do Ceará.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Sofia Almeida</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Achei o açaí muito doce para o paladar português. Meu marido brasileiro amou, eu nem tanto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Mariana Prata</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Ambiente lindo, atendimento cortês. Só a fila aos sábados que é uma loucura, uns 30 min de espera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>André Fernandes</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Melhor açaí de Portugal, sem dúvidas. Tenho vindo toda semana desde que abriu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Patrícia Nogueira</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Preço muito alto comparado ao do Brasil. Um bowl médio aqui custa quase 12 euros, absurdo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo Sá</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
           <t>Sorbet vem duro às vezes, precisa esperar. Sabor é ótimo, atendimento também.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Beatriz Costa</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Levei minha família portuguesa, todos experimentaram cupuaçu pela primeira vez. Ficaram encantados. Excelente iniciativa da marca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Rui Tavares</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Sabor bom mas o preço em euros é proibitivo. 11 euros num bowl é dinheiro que dá pra jantar num sítio decente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Carla Sousa</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Loja bem posicionada no shopping. Atendimento simpático. A doçura ainda é um ponto a ajustar pro paladar local.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Ribeiro</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Fui recomendado por amigo brasileiro. Cupuaçu virou obsessão. Preço é alto mas vale a experiência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Isabel Pinto</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Sábado 18h, fila de 40 min. Volume não corresponde à capacidade de atendimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Cardoso</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Bowl é único em Portugal — nenhuma outra loja tem cupuaçu assim. Preço em euros pesa, mas o produto compensa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Helena Gomes</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Comprei pra minha filha experimentar sabores brasileiros. Ela adorou o cupuaçu. Voltaremos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Vasconcelos</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Sábado impossível de vir, fila até fora do shopping. Prefiro sextas — mas aí muitas opções esgotam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Lopes</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Adoro o cupuaçu. Só o preço em euros que continua sendo um desafio, principalmente pra quem vem em família.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Tiago Barbosa</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Melhor abertura de food service em Lisboa em 2025. Cupuaçu virou o produto favorito da minha esposa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Sara Andrade</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Sorbet duro persistente. Sempre preciso esperar 5-10 min pra comer. Isso não deveria acontecer numa loja premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Filipa Neves</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Ambiente aconchegante, atendimento cortês. Preço é o único ponto — 12€ num bowl é o preço de um almoço em Lisboa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>José Antunes</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu com castanha-do-pará é uma revelação em Portugal. Parabéns pela expansão internacional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Maria João Costa</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Muito doce pro meu paladar. Meu marido brasileiro adorou. Talvez adaptar uma versão low-sugar pro público local?</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Sousa</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu é a estrela. Sabor autêntico do Brasil aqui em Lisboa. Vale cada centavo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Ana Filipa</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Fila enorme aos sábados. Vim 3 vezes, todas esperei mais de 25 min. Precisam melhorar a operação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Duarte Correia</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Loja bem cuidada, atendimento profissional. Preço alto mas justifica a qualidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Vera Mota</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Melhor doce que abriu em Lisboa nos últimos anos. Cupuaçu é obra-prima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Ferreira</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Sabor bom mas preço proibitivo pra frequência semanal. 12 euros é muito pra doce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Rita Machado</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Amei o cupuaçu, atendimento simpático. Sorbet vem gelado demais às vezes, mas nada que impossibilite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Alexandre Torres</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Trouxe meus pais brasileiros que estão de visita. Choraram de saudade comendo cupuaçu aqui. Isso é levar cultura junto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Inês Coelho</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Preço em euros continua sendo o grande problema. Se abrirem em Cascais ou Sintra com preços mais acessíveis, o crescimento seria explosivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Bettencourt</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Sabor bom, loja bonita, fluxo alto. Preço é caro mas único player com esse produto — segura o valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Iguatemi Lisboa</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa/PT</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Diana Ferraz</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Cupuaçu tá redefinindo padrões de doce em Lisboa. Continuem inovando.</t>
         </is>
       </c>
     </row>
